--- a/artfynd/A 72592-2021 artfynd.xlsx
+++ b/artfynd/A 72592-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 72592-2021 artfynd.xlsx
+++ b/artfynd/A 72592-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78653594</v>
+        <v>72469281</v>
       </c>
       <c r="B2" t="n">
-        <v>99382</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,30 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221223</v>
+        <v>220320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Ängsskära</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Serratula tinctoria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -723,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565503.9900154542</v>
+        <v>565504</v>
       </c>
       <c r="R2" t="n">
-        <v>6466686.849724905</v>
+        <v>6466687</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -753,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,9 +762,14 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Triviallövskog i branter</t>
+        </is>
+      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>lövskogslund</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,32 +787,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78981335</v>
+        <v>78653599</v>
       </c>
       <c r="B3" t="n">
-        <v>101219</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221978</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bergjohannesört</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypericum montanum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,19 +815,11 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -857,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565503.9900154542</v>
+        <v>565504</v>
       </c>
       <c r="R3" t="n">
-        <v>6466686.849724905</v>
+        <v>6466687</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,22 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +880,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vid bergbrant</t>
+          <t>lövskogslund</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78981692</v>
+        <v>78653594</v>
       </c>
       <c r="B4" t="n">
-        <v>108203</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>102225</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219716</v>
+        <v>221223</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,17 +937,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Odensgölvägen, Målstena 600m NO, Ög</t>
+          <t>Odensgölvägen, Målstena 500m NO, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565680.6751654235</v>
+        <v>565504</v>
       </c>
       <c r="R4" t="n">
-        <v>6466660.383177865</v>
+        <v>6466687</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,22 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,9 +989,9 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>lövskogslund</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1061,32 +1009,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78653599</v>
+        <v>78981335</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>103647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220785</v>
+        <v>221978</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Bergjohannesört</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hypericum montanum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1094,11 +1037,19 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1109,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565503.9900154542</v>
+        <v>565504</v>
       </c>
       <c r="R5" t="n">
-        <v>6466686.849724905</v>
+        <v>6466687</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1139,22 +1090,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1110,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>lövskogslund</t>
+          <t>Vid bergbrant</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1187,15 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>72469281</v>
+        <v>78981692</v>
       </c>
       <c r="B6" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>111399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,41 +1139,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220320</v>
+        <v>219716</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Krusfrö</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Selinum carvifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Odensgölvägen, Målstena 500m NO, Ög</t>
+          <t>Odensgölvägen, Målstena 600m NO, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565503.9900154542</v>
+        <v>565681</v>
       </c>
       <c r="R6" t="n">
-        <v>6466686.849724905</v>
+        <v>6466660</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1261,22 +1201,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,11 +1220,6 @@
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
-        <is>
-          <t>Triviallövskog i branter</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
         <is>
           <t>Vägkant</t>
         </is>
@@ -1317,12 +1242,7 @@
         <v>78981311</v>
       </c>
       <c r="B7" t="n">
-        <v>107008</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>110117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565680.6751654235</v>
+        <v>565681</v>
       </c>
       <c r="R7" t="n">
-        <v>6466660.383177865</v>
+        <v>6466660</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1403,19 +1323,9 @@
           <t>2019-07-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-07-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 72592-2021 artfynd.xlsx
+++ b/artfynd/A 72592-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78981692</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72469281</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78981311</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78653599</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78653594</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,8 +1385,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78981335</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>